--- a/quality_surveys/031_quality_control_process_feedback_questionnaire--quality_surveys.xlsx
+++ b/quality_surveys/031_quality_control_process_feedback_questionnaire--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Quality Control Process Feedback</t>
+          <t>What is the quality control process feedback?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quality_control_process</t>
+          <t>Which of the following best describes your quality control process?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Employee Feedback</t>
+          <t>What is your feedback about the employee feedback provided?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>issue_category</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Which category best describes the issue you are reporting?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>issue_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Please provide a date for the issue reported.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>issue_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>What is the location of the issue?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Which department is responsible for the quality control process?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Please provide your employee name.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>employee_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>What is your email?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,81 +750,81 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Is there any additional comment about the issue?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Which users submitted this report?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>submitted_on</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>When was the report submitted?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>At what time was the report submitted?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,63 +837,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submitted On</t>
+          <t>What category is this report under?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submitted At</t>
+          <t>Which department is this report under?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>submitted_users</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Submitted Users</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>submitted_time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>At what time was this report submitted?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>submitted_date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>When was this report submitted?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>submitted_at_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Submitted At 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>additional_comment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Any additional comments?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_category</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Which category is this report under?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>submitted_by_department</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submitted On</t>
+          <t>Submitted By Department</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>submitted_by_users</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submitted At</t>
+          <t>Submitted By Users</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,16 +1072,108 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>submitted_by_date</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Submitted By Date</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>submitted_by_time</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Submitted By Time</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>submitted_by_category_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Submitted By Category 2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>submitted_by_department_2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Submitted By Department 2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>submitted_by_2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Submitted By 2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1190,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1223,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1240,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
@@ -1165,63 +1257,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>compliance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>issue_category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quality'}</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Quality'}</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>issue_category_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'safety'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Safety'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>issue_category_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'compliance'}</t>
+          <t>compliance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Compliance'}</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1325,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quality_assurance'}</t>
+          <t>quality_assurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Quality Assurance'}</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quality_control'}</t>
+          <t>quality_control</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Quality Control'}</t>
+          <t>Quality Control</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1359,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'production'}</t>
+          <t>production</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Production'}</t>
+          <t>Production</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1376,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1393,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1410,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1427,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quality'}</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Quality'}</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1444,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'safety'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Safety'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
@@ -1369,267 +1461,675 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'compliance'}</t>
+          <t>compliance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Compliance'}</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quality_assurance'}</t>
+          <t>quality_assurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Quality Assurance'}</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quality_control'}</t>
+          <t>quality_control</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Quality Control'}</t>
+          <t>Quality Control</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'production'}</t>
+          <t>production</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Production'}</t>
+          <t>Production</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_users_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_users_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_users_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>submitted_on_choices</t>
+          <t>submitted_time_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'date_1'}</t>
+          <t>time_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Date 1'}</t>
+          <t>Time 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>submitted_on_choices</t>
+          <t>submitted_time_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'date_2'}</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Date 2'}</t>
+          <t>Time 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>submitted_on_choices</t>
+          <t>submitted_time_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'date_3'}</t>
+          <t>time_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Date 3'}</t>
+          <t>Time 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>submitted_at_choices</t>
+          <t>submitted_date_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'time_1'}</t>
+          <t>date_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Time 1'}</t>
+          <t>Date 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>submitted_at_choices</t>
+          <t>submitted_date_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'time_2'}</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Time 2'}</t>
+          <t>Date 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>submitted_at_choices</t>
+          <t>submitted_date_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'time_3'}</t>
+          <t>date_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Time 3'}</t>
+          <t>Date 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>submitted_at_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quality'}</t>
+          <t>time_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Quality'}</t>
+          <t>Time 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>submitted_at_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'safety'}</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Safety'}</t>
+          <t>Time 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>submitted_at_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'compliance'}</t>
+          <t>time_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Compliance'}</t>
+          <t>Time 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>submitted_by_category_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>submitted_by_category_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>submitted_by_category_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>submitted_by_department_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>quality_assurance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>submitted_by_department_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>quality_control</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quality Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>submitted_by_department_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>submitted_by_users_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>user_1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>User 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>submitted_by_users_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>user_2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>User 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>submitted_by_users_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>user_3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>User 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>submitted_by_date_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>date_1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Date 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>submitted_by_date_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>date_2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Date 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>submitted_by_date_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>date_3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Date 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>submitted_by_time_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>time_1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Time 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>submitted_by_time_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>time_2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Time 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>submitted_by_time_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>time_3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Time 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>submitted_by_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>submitted_by_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>submitted_by_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>submitted_by_department_2_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>quality_assurance</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>submitted_by_department_2_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>quality_control</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Quality Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>submitted_by_department_2_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>submitted_by_2_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>user_1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>User 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>submitted_by_2_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>user_2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>User 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>submitted_by_2_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>user_3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>User 3</t>
         </is>
       </c>
     </row>
